--- a/code/data_management/meta_data_processing.xlsx
+++ b/code/data_management/meta_data_processing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute-my.sharepoint.com/personal/sue_su_alleninstitute_org/Documents/LCpaper/manuscript/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="316" documentId="8_{13714737-15D5-6D46-9EE3-176A3926FE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D177E89F-554C-436C-BDD0-F496F4CD7A1A}"/>
+  <xr:revisionPtr revIDLastSave="238" documentId="8_{13714737-15D5-6D46-9EE3-176A3926FE2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0E32813F-12B6-3B41-BCB4-D9C84C09F182}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="7125" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{FFE2B52C-1751-7945-8601-5DA37AD336B9}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="30240" windowHeight="17740" activeTab="4" xr2:uid="{FFE2B52C-1751-7945-8601-5DA37AD336B9}"/>
   </bookViews>
   <sheets>
     <sheet name="sessions" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,8 @@
     <sheet name="all_ccf" sheetId="4" r:id="rId4"/>
     <sheet name="all_dorsal_edge" sheetId="5" r:id="rId5"/>
     <sheet name="all_FP_location" sheetId="6" r:id="rId6"/>
-    <sheet name="np_spatial_crosscorr" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="64">
   <si>
     <t>name</t>
   </si>
@@ -77,6 +76,12 @@
     <t>compute_raw_waveforms</t>
   </si>
   <si>
+    <t>ephys/opto/curated</t>
+  </si>
+  <si>
+    <t>ephys/curated/processed</t>
+  </si>
+  <si>
     <t>ephys/opto/curated/opto_waveforms.zarr</t>
   </si>
   <si>
@@ -134,9 +139,15 @@
     <t>ephys/curated/processed/ccf_unit_locations.csv</t>
   </si>
   <si>
+    <t>ephys/opto/curated/{session_id}_curated_soma_opto_tagging_summary.pkl</t>
+  </si>
+  <si>
     <t>ephys/opto/curated/{session_id}_opto_sigs.pkl</t>
   </si>
   <si>
+    <t>ephys/opto/curated/{session_id}_antidromic_results.pkl</t>
+  </si>
+  <si>
     <t>trial_wise_drift_computation</t>
   </si>
   <si>
@@ -185,6 +196,9 @@
     <t>\</t>
   </si>
   <si>
+    <t>https://github.com/AllenNeuralDynamics/ibl-ephys-alignment-gui/tree/882940b7e34bf63c939ab67e8307cfba0fa388f9</t>
+  </si>
+  <si>
     <t>src/ephys_alignment_gui/launch_gui.py</t>
   </si>
   <si>
@@ -206,6 +220,12 @@
     <t>code/beh_ephys_analysis/beh_metrics.py</t>
   </si>
   <si>
+    <t>https://github.com/AllenNeuralDynamics/ccf_annotations_data_prep/blob/main/code/check_L_R.ipynb</t>
+  </si>
+  <si>
+    <t>https://github.com/AllenNeuralDynamics/ccf_annotations_data_prep/blob/main</t>
+  </si>
+  <si>
     <t>convert_manual_annotation2ccf</t>
   </si>
   <si>
@@ -213,57 +233,6 @@
   </si>
   <si>
     <t xml:space="preserve">Manual annotation of dorsal edge of LC is performed in neuraglancer and converted here to ccf coordinates. </t>
-  </si>
-  <si>
-    <t>version</t>
-  </si>
-  <si>
-    <t>882940b7e34bf63c939ab67e8307cfba0fa388f9</t>
-  </si>
-  <si>
-    <t>https://github.com/AllenNeuralDynamics/ibl-ephys-alignment-gui</t>
-  </si>
-  <si>
-    <t>764145811bfd21b4d06cfe39e59217082d69d76a</t>
-  </si>
-  <si>
-    <t>https://github.com/AllenNeuralDynamics/ccf_annotations_data_prep</t>
-  </si>
-  <si>
-    <t>ephys/opto/curated/drift,ephys/opto/curated/{session_id}_opto_drift_tbl.csv,ephys/opto/curated/{session_id}_opto_drift_tbl.csv,ephys/opto/curated/{session_id}_motion_drift.pdf,ephys/opto/curated/ {session_id}_drift.pdf</t>
-  </si>
-  <si>
-    <t>ephys/opto/curated/{session_id}_antidromic_results.pkl,ephys/opto/curated/figures/antidromic</t>
-  </si>
-  <si>
-    <t>ephys/opto/curated/figures,ephys/opto/curated/{session_id}_opto_tagging_metrics.pkl,ephys/opto/curated/{session_id}_opto_waveform_metrics.pkl,ephys/opto/curated/{session_id}_opto_tagging.pdf</t>
-  </si>
-  <si>
-    <t>ephys/opto/curated/{session_id}_curated_soma_opto_tagging_summary.pkl,ephys/opto/curated/{session_id}_curated_soma_opto_summary.pdf</t>
-  </si>
-  <si>
-    <t>ephys/curated/processed/{session_id}_curated_auto_corr.pkl,ephys/curated/processed/{session_id}_curated_cross_corr.pkl,ephys/curated/processed/{session_id}_curated_long_corr.png,ephys/curated/processed/{session_id}_curated_short_corr.png</t>
-  </si>
-  <si>
-    <t>{animal_id}_glm_choice_history_model_results.pdf,glm_choice_history_model_results.pkl</t>
-  </si>
-  <si>
-    <t>code/beh_ephys_analysis/lick_video_analysis.py</t>
-  </si>
-  <si>
-    <t>lick_in_trial_model_coefficients_video_False.pdf,lick_in_trial_model_coefficients_video_True.pdf,lick_in_trial_model_coefficients.pdf,lick_in_trial_model_video_False.pkl,lick_in_trial_model_video_True.pkl,lick_train_stats_video_False.pkl,lick_train_stats_video_True.pkl,lick_train_stats.pkl,lick_trains_video_False.pdf,lick_trains_video_True.pdf,lick_trains.pdf</t>
-  </si>
-  <si>
-    <t>clean_up_lick_video_segments</t>
-  </si>
-  <si>
-    <t>compute_spatial_crosscorr</t>
-  </si>
-  <si>
-    <t>band_corr</t>
-  </si>
-  <si>
-    <t>code/beh_ephys_analysis/ephys_spatial_feature.py</t>
   </si>
 </sst>
 </file>
@@ -306,15 +275,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
+      <sz val="18"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color theme="1"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -365,7 +334,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -389,15 +358,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -414,6 +392,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -734,17 +716,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1772B6F7-3758-5747-BB67-BFF3A7BA4434}">
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="47" customWidth="1"/>
-    <col min="2" max="2" width="63.8125" customWidth="1"/>
-    <col min="3" max="3" width="35.125" customWidth="1"/>
-    <col min="4" max="4" width="23.1875" style="8" customWidth="1"/>
+    <col min="2" max="2" width="63.83203125" customWidth="1"/>
+    <col min="3" max="3" width="35.1640625" customWidth="1"/>
+    <col min="4" max="4" width="23.1640625" style="8" customWidth="1"/>
     <col min="5" max="5" width="44" customWidth="1"/>
-    <col min="6" max="6" width="40.25" customWidth="1"/>
+    <col min="6" max="6" width="40.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -752,7 +734,7 @@
         <v>3</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>1</v>
@@ -761,188 +743,188 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.7">
+    <row r="2" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
-      <c r="A7" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="B7" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.65">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="1" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="A12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.7">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>57</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.5"/>
+        <v>14</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="50" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{23ECD49E-201B-3840-A84D-6A40CA277E94}"/>
@@ -953,23 +935,22 @@
     <hyperlink ref="D13" r:id="rId6" xr:uid="{E9017DD4-36DD-4F45-BB17-7B59F59BC27A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57EB3044-9E2B-DC46-A8B2-1DB9ED99F9B2}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="39.6875" customWidth="1"/>
-    <col min="2" max="2" width="32.3125" customWidth="1"/>
+    <col min="1" max="1" width="39.6640625" customWidth="1"/>
+    <col min="2" max="2" width="32.33203125" customWidth="1"/>
     <col min="3" max="3" width="29" customWidth="1"/>
-    <col min="4" max="4" width="58.8125" customWidth="1"/>
-    <col min="5" max="5" width="34.6875" customWidth="1"/>
+    <col min="4" max="4" width="58.83203125" customWidth="1"/>
+    <col min="5" max="5" width="34.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5" ht="25" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -977,7 +958,7 @@
         <v>3</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>1</v>
@@ -986,46 +967,46 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.5">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
         <v>40</v>
       </c>
-      <c r="B4" t="s">
-        <v>36</v>
-      </c>
       <c r="D4" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1035,18 +1016,18 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79812901-A6B2-564A-98EF-B6EC9A0AF142}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="50.1875" customWidth="1"/>
-    <col min="3" max="3" width="22.6875" customWidth="1"/>
-    <col min="4" max="4" width="83.8125" customWidth="1"/>
-    <col min="5" max="5" width="31.1875" customWidth="1"/>
-    <col min="6" max="6" width="24.6875" customWidth="1"/>
+    <col min="2" max="2" width="50.1640625" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" customWidth="1"/>
+    <col min="4" max="4" width="83.83203125" customWidth="1"/>
+    <col min="5" max="5" width="31.1640625" customWidth="1"/>
+    <col min="6" max="6" width="24.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="23.25" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5" ht="25" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1054,7 +1035,7 @@
         <v>3</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>1</v>
@@ -1063,58 +1044,41 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="A3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{0027B72A-6E20-6348-8387-03E21E5D1773}"/>
-    <hyperlink ref="D3" r:id="rId2" xr:uid="{DC1E97AC-7234-4E30-B624-EB37CCB5165E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F465CB9-37DB-5742-8039-98F9D3D791D6}">
-  <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:E21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.1875" customWidth="1"/>
-    <col min="2" max="2" width="19.0625" customWidth="1"/>
-    <col min="3" max="3" width="20.0625" customWidth="1"/>
-    <col min="4" max="4" width="61.5625" customWidth="1"/>
-    <col min="5" max="5" width="34.5" customWidth="1"/>
-    <col min="6" max="6" width="38.25" customWidth="1"/>
+    <col min="1" max="1" width="22.1640625" customWidth="1"/>
+    <col min="2" max="2" width="37.83203125" customWidth="1"/>
+    <col min="3" max="3" width="43.5" customWidth="1"/>
+    <col min="4" max="4" width="71.6640625" customWidth="1"/>
+    <col min="5" max="5" width="40.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5" ht="25" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1122,7 +1086,7 @@
         <v>3</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>1</v>
@@ -1130,33 +1094,32 @@
       <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D2" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C21" t="s">
         <v>59</v>
-      </c>
-      <c r="E2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.5">
-      <c r="C20" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" t="s">
-        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1164,60 +1127,53 @@
     <hyperlink ref="D2" r:id="rId1" xr:uid="{98AE4375-52C5-8943-BF9E-A8DC1E11B69F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B2AA6A6-C8DA-AF48-AC98-394E26C99DD1}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="39.6875" customWidth="1"/>
-    <col min="2" max="2" width="25.625" customWidth="1"/>
-    <col min="3" max="3" width="58.375" customWidth="1"/>
-    <col min="4" max="4" width="29.6875" customWidth="1"/>
-    <col min="5" max="5" width="35.5625" customWidth="1"/>
+    <col min="1" max="1" width="39.6640625" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="94.1640625" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="47.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.5">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" ht="25" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="C1" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="F2" t="s">
         <v>60</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1225,70 +1181,14 @@
     <hyperlink ref="D2" r:id="rId1" xr:uid="{B08C88E9-908A-F447-B1DC-4B10229D2AF8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B436F805-BB62-4849-8671-E3858B17BED0}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37CCC006-4539-441B-882C-29E49D287785}">
-  <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.5"/>
-  <cols>
-    <col min="1" max="1" width="23" customWidth="1"/>
-    <col min="2" max="2" width="15.25" customWidth="1"/>
-    <col min="3" max="3" width="20.8125" customWidth="1"/>
-    <col min="4" max="4" width="37.75" customWidth="1"/>
-    <col min="5" max="5" width="42.5" customWidth="1"/>
-    <col min="6" max="6" width="21.0625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.5">
-      <c r="A1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.5">
-      <c r="A2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{27FFD22E-7285-4055-A0E1-76D6E9947BBB}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>